--- a/tests/fixtures/etat_stock.xlsx
+++ b/tests/fixtures/etat_stock.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -47,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +510,61 @@
           <t>CLASS CODE</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>QTE CONSO 12M</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>QTE CONSO 18M</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>QTE CONSO 24M</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>QTE CONSO 2021</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>QTE CONSO 2022</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>QTE CONSO 2023</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>QTE CONSO 2024</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>QTE CONSO 2025</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Dernier PU (achat) Euros</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>B/O</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>DATE DERNIERE CONSO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -549,6 +607,39 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>25</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1" t="n">
+        <v>46266</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -591,6 +682,39 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
+      <c r="K3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>46266</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -633,6 +757,39 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
+      <c r="K4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L4" t="n">
+        <v>40</v>
+      </c>
+      <c r="M4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20</v>
+      </c>
+      <c r="O4" t="n">
+        <v>25</v>
+      </c>
+      <c r="P4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>35</v>
+      </c>
+      <c r="R4" t="n">
+        <v>45</v>
+      </c>
+      <c r="S4" t="n">
+        <v>60</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>46296</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -675,6 +832,39 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
+      <c r="K5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>46266</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -717,6 +907,39 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>46266</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -759,6 +982,39 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
+        <v>8</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>46266</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -801,6 +1057,39 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>46266</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -838,6 +1127,39 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>46266</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -880,6 +1202,39 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>46266</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -922,6 +1277,39 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>46266</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -963,6 +1351,39 @@
       </c>
       <c r="J12" t="n">
         <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>46266</v>
       </c>
     </row>
     <row r="13">
@@ -1004,6 +1425,39 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>46266</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1046,6 +1500,39 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>46266</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1087,6 +1574,189 @@
       </c>
       <c r="J15" t="n">
         <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10</v>
+      </c>
+      <c r="O15" t="n">
+        <v>8</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FX-2001</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Housse dormante</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>245</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AG05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>F020</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fournisseur Papa</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>120</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>43586</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FX-2002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rideau inactif</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>245</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AG05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>F021</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Fournisseur Quebec</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>31</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>80</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>36892</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/etat_stock.xlsx
+++ b/tests/fixtures/etat_stock.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,11 @@
           <t>DATE DERNIERE CONSO</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>TRACKING LEVEL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -640,6 +645,11 @@
       <c r="U2" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>TL1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -715,6 +725,11 @@
       <c r="U3" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -790,6 +805,11 @@
       <c r="U4" s="1" t="n">
         <v>46296</v>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TL1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -865,6 +885,11 @@
       <c r="U5" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -940,6 +965,11 @@
       <c r="U6" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>TL1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1015,6 +1045,11 @@
       <c r="U7" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1090,6 +1125,11 @@
       <c r="U8" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1160,6 +1200,11 @@
       <c r="U9" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1235,6 +1280,11 @@
       <c r="U10" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1310,6 +1360,11 @@
       <c r="U11" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1384,6 +1439,11 @@
       </c>
       <c r="U12" s="1" t="n">
         <v>46266</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TL1</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1458,6 +1518,11 @@
       <c r="U13" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1533,6 +1598,11 @@
       <c r="U14" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1608,6 +1678,11 @@
       <c r="U15" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TL1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1683,6 +1758,11 @@
       <c r="U16" s="1" t="n">
         <v>43586</v>
       </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TL1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1757,6 +1837,11 @@
       </c>
       <c r="U17" s="1" t="n">
         <v>36892</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/etat_stock.xlsx
+++ b/tests/fixtures/etat_stock.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1844,6 +1844,566 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FM-1001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FOAM BOTTOM J</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>40</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>245</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>AG06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>F030</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Fournisseur Sierra</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>60</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" t="n">
+        <v>15</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20</v>
+      </c>
+      <c r="N18" t="n">
+        <v>10</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>10</v>
+      </c>
+      <c r="R18" t="n">
+        <v>10</v>
+      </c>
+      <c r="S18" t="n">
+        <v>180</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>TL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FM-1002</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FOAM BACKREST J</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>245</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AG06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>F030</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Fournisseur Sierra</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" t="n">
+        <v>15</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20</v>
+      </c>
+      <c r="N19" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" t="n">
+        <v>10</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
+        <v>10</v>
+      </c>
+      <c r="S19" t="n">
+        <v>150</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FM-1003</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FOAM BOTT W</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>245</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>AG06</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>F031</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Fournisseur Tango</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" t="n">
+        <v>15</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20</v>
+      </c>
+      <c r="N20" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" t="n">
+        <v>10</v>
+      </c>
+      <c r="P20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>10</v>
+      </c>
+      <c r="R20" t="n">
+        <v>10</v>
+      </c>
+      <c r="S20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>TL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FM-1004</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FOAM BOTTOM Y</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>300</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>245</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>AG06</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>F031</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Fournisseur Tango</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>60</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" t="n">
+        <v>15</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20</v>
+      </c>
+      <c r="N21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" t="n">
+        <v>10</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>10</v>
+      </c>
+      <c r="R21" t="n">
+        <v>10</v>
+      </c>
+      <c r="S21" t="n">
+        <v>45</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FM-2001</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FOAM BOTTOM SEAT J</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>245</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>AG06</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>F030</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Fournisseur Sierra</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>60</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L22" t="n">
+        <v>15</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" t="n">
+        <v>10</v>
+      </c>
+      <c r="P22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>10</v>
+      </c>
+      <c r="R22" t="n">
+        <v>10</v>
+      </c>
+      <c r="S22" t="n">
+        <v>175</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>TL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FM-2002</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FOAM BACKREST J</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>245</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>AG06</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>F032</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Fournisseur Uniform</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>60</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>10</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10</v>
+      </c>
+      <c r="O23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" t="n">
+        <v>10</v>
+      </c>
+      <c r="S23" t="n">
+        <v>140</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TL0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FM-2003</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FOAM BOTT W</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>245</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>AG06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>F031</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Fournisseur Tango</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>60</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>10</v>
+      </c>
+      <c r="L24" t="n">
+        <v>15</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>10</v>
+      </c>
+      <c r="P24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>10</v>
+      </c>
+      <c r="R24" t="n">
+        <v>10</v>
+      </c>
+      <c r="S24" t="n">
+        <v>85</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TL1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/fixtures/etat_stock.xlsx
+++ b/tests/fixtures/etat_stock.xlsx
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>60</v>
+        <v>7101</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>60</v>
+        <v>7102</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>60</v>
+        <v>7103</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>60</v>
+        <v>7104</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>60</v>
+        <v>7201</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>60</v>
+        <v>7202</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>60</v>
+        <v>7203</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>

--- a/tests/fixtures/etat_stock.xlsx
+++ b/tests/fixtures/etat_stock.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,16 @@
           <t>TRACKING LEVEL</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>QTE SAR</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Purchase Req.</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -650,6 +660,12 @@
           <t>TL1</t>
         </is>
       </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -730,6 +746,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -810,6 +832,12 @@
           <t>TL1</t>
         </is>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -890,6 +918,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -970,6 +1004,12 @@
           <t>TL1</t>
         </is>
       </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1050,6 +1090,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1130,6 +1176,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1205,6 +1257,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1285,6 +1343,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1365,6 +1429,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1444,6 +1514,12 @@
         <is>
           <t>TL1</t>
         </is>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1523,6 +1599,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1603,6 +1685,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1683,6 +1771,12 @@
           <t>TL1</t>
         </is>
       </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1763,6 +1857,12 @@
           <t>TL1</t>
         </is>
       </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1843,6 +1943,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1923,6 +2029,12 @@
           <t>TL1</t>
         </is>
       </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2003,6 +2115,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2083,6 +2201,12 @@
           <t>TL1</t>
         </is>
       </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2163,6 +2287,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2243,6 +2373,12 @@
           <t>TL1</t>
         </is>
       </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2323,6 +2459,12 @@
           <t>TL0</t>
         </is>
       </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2402,6 +2544,12 @@
         <is>
           <t>TL1</t>
         </is>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
